--- a/data/trending_integrated_20261029_14.xlsx
+++ b/data/trending_integrated_20261029_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>5080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.57%</t>
+          <t>'+29.10%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>7489914070</v>
+        <v>7577897160</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9120</v>
+        <v>9140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.14%</t>
+          <t>'+14.39%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>132014942040</v>
+        <v>133171784950</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37850</v>
+        <v>38050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.76%</t>
+          <t>'+9.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>114380297825</v>
+        <v>114990297975</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -854,13 +854,13 @@
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>111388467040</v>
+        <v>111851997275</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1533000</v>
+        <v>1547000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G6" t="n">
-        <v>1543</v>
+        <v>1589</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5502096871000</v>
+        <v>5591036857000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자와 분리된 주가 흐름 전망. 4분기 실적 기대감 및 높은 주주환원율 강조.</t>
+          <t>긍정적 실적 전망 및 타사 대비 높은 배당금 언급. 삼성전자와의 비교 우위 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하이닉스', '주주환원', '실적']</t>
+          <t>['실적 전망', '배당금', '어닝콜']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29050</v>
+        <v>14710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28700</v>
+        <v>14390</v>
       </c>
       <c r="K7" t="n">
-        <v>29150</v>
+        <v>15450</v>
       </c>
       <c r="L7" t="n">
-        <v>31400</v>
+        <v>16290</v>
       </c>
       <c r="M7" t="n">
-        <v>28350</v>
+        <v>14040</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>106537069600</v>
+        <v>55379863530</v>
       </c>
       <c r="P7" t="n">
-        <v>59600</v>
+        <v>49800</v>
       </c>
       <c r="Q7" t="n">
-        <v>1850</v>
+        <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>-52000</v>
+        <v>-290000</v>
       </c>
       <c r="S7" t="n">
-        <v>10000</v>
+        <v>-6000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>의료 AI 섹터 전반의 조정 및 공매도 압력 속 하락세 지속. 매수 구간 논란.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['의료 AI', '공매도', '매수 구간']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14510</v>
+        <v>29200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.83%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>28700</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>29150</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>31400</v>
       </c>
       <c r="M8" t="n">
-        <v>14040</v>
+        <v>28350</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>54711675765</v>
+        <v>107079886500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>59600</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>1850</v>
       </c>
       <c r="R8" t="n">
-        <v>-290000</v>
+        <v>-52000</v>
       </c>
       <c r="S8" t="n">
-        <v>-6000</v>
+        <v>10000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 의료AI 기업 급등 속 루닛 주가 변동성 확대. 단기 차익 실현 매물 출회 및 공매도 언급.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '차익실현']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>537000</v>
+        <v>540000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+1.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F9" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G9" t="n">
-        <v>1839</v>
+        <v>1813</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>515312948500</v>
+        <v>523771049500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 반영.</t>
+          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '컨퍼런스콜', '전고체배터리']</t>
+          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14880</v>
+        <v>15000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'+0.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" t="n">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>145373604620</v>
+        <v>146090619755</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63200</v>
+        <v>63100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="H11" t="n">
         <v>41.55</v>
@@ -1438,7 +1438,7 @@
         <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>168723320050</v>
+        <v>170789170950</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 관련 긍정적 언급. 수소 시대 도래에 따른 성장 전망 및 신고가 근접.</t>
+          <t>자사주 매입 및 소각 이슈 부각. 수소 관련 사업 기대감 및 신고가 근접 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주', '수주', '신고가']</t>
+          <t>['자사주 소각', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>184400</v>
+        <v>185900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H12" t="n">
         <v>75</v>
@@ -1530,7 +1530,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1304838622400</v>
+        <v>1325716107050</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8890</v>
+        <v>8970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30781329195</v>
+        <v>30919893235</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15955</v>
+        <v>15930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-3.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F14" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G14" t="n">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="H14" t="n">
         <v>28.07</v>
@@ -1714,7 +1714,7 @@
         <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>57656528910</v>
+        <v>59514747620</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25450</v>
+        <v>231750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.68%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>105</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>511</v>
       </c>
       <c r="G15" t="n">
-        <v>382</v>
+        <v>2860</v>
       </c>
       <c r="H15" t="n">
-        <v>12.23</v>
+        <v>46.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,130 +1791,130 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>26700</v>
+        <v>242000</v>
       </c>
       <c r="K15" t="n">
-        <v>26350</v>
+        <v>241000</v>
       </c>
       <c r="L15" t="n">
-        <v>26600</v>
+        <v>249000</v>
       </c>
       <c r="M15" t="n">
-        <v>24400</v>
+        <v>226000</v>
       </c>
       <c r="N15" t="n">
-        <v>12.3</v>
+        <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>58314373525</v>
+        <v>4685092305750</v>
       </c>
       <c r="P15" t="n">
-        <v>59300</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>22000</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>-142000</v>
+        <v>-434000</v>
       </c>
       <c r="S15" t="n">
-        <v>-15000</v>
+        <v>-387000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 발표 앞두고 혼조세. 태양광 부문 전망 및 원전 관련 이슈 언급.</t>
+          <t>이재용 관련 부정적 여론과 증여세 이슈 부각. 주가 부양 전략 부재 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광', '원전']</t>
+          <t>['증여세', '국정조사', '주주환원']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>229500</v>
+        <v>4000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.17%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>518</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>2667</v>
+        <v>391</v>
       </c>
       <c r="H16" t="n">
-        <v>46.19</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>242000</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>241000</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>249000</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>226000</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4611680092500</v>
+        <v>167251070868</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-434000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-387000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 증여세 관련 주가 하락 언급. 노조 및 임원진 비판과 국정조사 요구.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,143 +1923,143 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['증여세', '국정조사', '주주환원']</t>
+          <t>['5G', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3965</v>
+        <v>56900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-7.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="G17" t="n">
-        <v>382</v>
+        <v>2063</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>22.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4195</v>
+        <v>61400</v>
       </c>
       <c r="K17" t="n">
-        <v>4280</v>
+        <v>60600</v>
       </c>
       <c r="L17" t="n">
-        <v>4480</v>
+        <v>60800</v>
       </c>
       <c r="M17" t="n">
-        <v>3915</v>
+        <v>53400</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2</v>
+        <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>166677551096</v>
+        <v>370040607800</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>-190000</v>
+        <v>-1454000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-731000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
+          <t>체코 원전 수주 관련 풍문 및 허위 기사로 인한 주가 하락. 회사 해명 공시에도 불신 지속.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '글로벌 공급']</t>
+          <t>['체코 원전', '풍문', '해명 공시']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55900</v>
+        <v>24500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.96%</t>
+          <t>'-8.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>2051</v>
+        <v>436</v>
       </c>
       <c r="H18" t="n">
-        <v>22.34</v>
+        <v>12.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>61400</v>
+        <v>26700</v>
       </c>
       <c r="K18" t="n">
-        <v>60600</v>
+        <v>26350</v>
       </c>
       <c r="L18" t="n">
-        <v>60800</v>
+        <v>26600</v>
       </c>
       <c r="M18" t="n">
-        <v>53400</v>
+        <v>24350</v>
       </c>
       <c r="N18" t="n">
-        <v>22.32</v>
+        <v>12.3</v>
       </c>
       <c r="O18" t="n">
-        <v>360362068850</v>
+        <v>76170217050</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>53400</v>
+        <v>22000</v>
       </c>
       <c r="R18" t="n">
-        <v>-1454000</v>
+        <v>-142000</v>
       </c>
       <c r="S18" t="n">
-        <v>-731000</v>
+        <v>-15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 협상 결렬 관련, 두산에너빌리티는 무관하다는 해명 공시. 허위 기사 및 풍문 논란.</t>
+          <t>실적 발표 앞두고 부정적 전망 우세. 태양광 사업 부진 및 적자 전환 가능성 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '공시', '협상']</t>
+          <t>['실적 발표', '적자 전환', '태양광']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>13874220520</v>
+        <v>13940565468</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16570</v>
+        <v>16820</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.74%</t>
+          <t>'-12.44%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>93681703200</v>
+        <v>94636781465</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 출회 우려로 인한 주가 급락 경고. 주포의 움직임에 대한 의구심.</t>
+          <t>보호예수 물량 출회 우려 및 주가 폭락 가능성 경고. 주포 이탈 및 투매 신호 감지.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '주포']</t>
+          <t>['보호예수', '주포', '폭락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11840</v>
+        <v>11970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-17.03%</t>
+          <t>'-16.12%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G21" t="n">
-        <v>2367</v>
+        <v>2383</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>329040394795</v>
+        <v>332464675225</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.70%</t>
+          <t>'-17.51%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16814439743</v>
+        <v>16890461592</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>

--- a/data/trending_integrated_20261029_14.xlsx
+++ b/data/trending_integrated_20261029_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.10%</t>
+          <t>'+27.57%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>7577897160</v>
+        <v>7689171280</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -619,7 +619,7 @@
         <v>2900</v>
       </c>
       <c r="R2" t="n">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9140</v>
+        <v>9320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.39%</t>
+          <t>'+16.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
         <v>107</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>133171784950</v>
+        <v>136629468410</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -711,10 +711,10 @@
         <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>-19000</v>
+        <v>-2000</v>
       </c>
       <c r="S3" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38050</v>
+        <v>38200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.34%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>114990297975</v>
+        <v>116139452925</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -803,10 +803,10 @@
         <v>15260</v>
       </c>
       <c r="R4" t="n">
-        <v>89000</v>
+        <v>79000</v>
       </c>
       <c r="S4" t="n">
-        <v>39000</v>
+        <v>44000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7880</v>
+        <v>7850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.77%</t>
+          <t>'+5.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>111851997275</v>
+        <v>112448771695</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -895,7 +895,7 @@
         <v>952</v>
       </c>
       <c r="R5" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1547000</v>
+        <v>1555000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+4.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="G6" t="n">
-        <v>1589</v>
+        <v>1645</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5591036857000</v>
+        <v>5721986952000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -987,23 +987,23 @@
         <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>357000</v>
+        <v>374000</v>
       </c>
       <c r="S6" t="n">
-        <v>-139000</v>
+        <v>-115000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>긍정적 실적 전망 및 타사 대비 높은 배당금 언급. 삼성전자와의 비교 우위 강조.</t>
+          <t>SK하이닉스 주가 상승에 대한 긍정적 전망. 삼성전자와의 차별화 언급. 외인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 전망', '배당금', '어닝콜']</t>
+          <t>['SK하이닉스', '주가 상승', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14710</v>
+        <v>14760</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.22%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>55379863530</v>
+        <v>56153129890</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1079,23 +1079,23 @@
         <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>-290000</v>
+        <v>-273000</v>
       </c>
       <c r="S7" t="n">
-        <v>-6000</v>
+        <v>-15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 전반의 조정 및 공매도 압력 속 하락세 지속. 매수 구간 논란.</t>
+          <t>의료 AI 관련 긍정적 뉴스에도 불구하고 주가 하락세 지속. 공매도 및 매물 출회 가능성 언급. 투자 주의 경고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '매수 구간']</t>
+          <t>['의료 AI', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29200</v>
+        <v>29350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+2.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
         <v>78</v>
@@ -1162,7 +1162,7 @@
         <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>107079886500</v>
+        <v>108165390300</v>
       </c>
       <c r="P8" t="n">
         <v>59600</v>
@@ -1171,10 +1171,10 @@
         <v>1850</v>
       </c>
       <c r="R8" t="n">
-        <v>-52000</v>
+        <v>-53000</v>
       </c>
       <c r="S8" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>540000</v>
+        <v>542000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.12%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G9" t="n">
-        <v>1813</v>
+        <v>1831</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>523771049500</v>
+        <v>531021923000</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1263,10 +1263,10 @@
         <v>259000</v>
       </c>
       <c r="R9" t="n">
-        <v>-39000</v>
+        <v>-36000</v>
       </c>
       <c r="S9" t="n">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15000</v>
+        <v>15080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>91</v>
       </c>
       <c r="G10" t="n">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>146090619755</v>
+        <v>148433131745</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1355,23 +1355,23 @@
         <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>-464000</v>
+        <v>-444000</v>
       </c>
       <c r="S10" t="n">
         <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타버스 관련 뉴스 및 루멘텀 인수설, 삼성전자 투자 가능성 제기. 연말 목표가 3만 제시.</t>
+          <t>메타, 유리기판 관련 뉴스 및 미국장 상승 영향. 루멘텀 인수 가능성 및 연금 매집. 삼성·SK 품질 안정화 기술 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메타버스', '루멘텀', '삼성전자']</t>
+          <t>['유리기판', '루멘텀', '품질 안정화']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63100</v>
+        <v>187200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.71%</t>
+          <t>'-1.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G11" t="n">
-        <v>693</v>
+        <v>586</v>
       </c>
       <c r="H11" t="n">
-        <v>41.55</v>
+        <v>75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>64200</v>
+        <v>190100</v>
       </c>
       <c r="K11" t="n">
-        <v>64200</v>
+        <v>189400</v>
       </c>
       <c r="L11" t="n">
-        <v>65500</v>
+        <v>197000</v>
       </c>
       <c r="M11" t="n">
-        <v>62500</v>
+        <v>180800</v>
       </c>
       <c r="N11" t="n">
-        <v>41.01</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>170789170950</v>
+        <v>1353538517750</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>243500</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>71000</v>
       </c>
       <c r="R11" t="n">
-        <v>436000</v>
+        <v>-1382000</v>
       </c>
       <c r="S11" t="n">
-        <v>-150000</v>
+        <v>-119000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 이슈 부각. 수소 관련 사업 기대감 및 신고가 근접 가능성 언급.</t>
+          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 부정적 전망. 우선주 매입 소각 기대감 있으나 확정적이지 않음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 소각', '수주 공시', '신고가']</t>
+          <t>['우선주', '주주환원', '오너 리스크']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>185900</v>
+        <v>63200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>570</v>
+        <v>691</v>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
+        <v>41.55</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>190100</v>
+        <v>64200</v>
       </c>
       <c r="K12" t="n">
-        <v>189400</v>
+        <v>64200</v>
       </c>
       <c r="L12" t="n">
-        <v>197000</v>
+        <v>65500</v>
       </c>
       <c r="M12" t="n">
-        <v>180800</v>
+        <v>62500</v>
       </c>
       <c r="N12" t="n">
-        <v>74.90000000000001</v>
+        <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1325716107050</v>
+        <v>172952677000</v>
       </c>
       <c r="P12" t="n">
-        <v>243500</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>71000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-1183000</v>
+        <v>273000</v>
       </c>
       <c r="S12" t="n">
-        <v>-148000</v>
+        <v>-191000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 부정적 전망. 우선주 매입 소각 기대감 있으나 확정적이지 않음.</t>
+          <t>자사주 소각 및 매입 지속. 수주 공시 및 신고가 도전 가능성 언급. 삼성전자 시설 투자 확대 수혜 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '오너 리스크']</t>
+          <t>['자사주 소각', '수주 공시', '삼성전자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8970</v>
+        <v>8930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-2.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30919893235</v>
+        <v>31020676725</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1631,10 +1631,10 @@
         <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-42000</v>
+        <v>-40000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15930</v>
+        <v>232500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.51%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>196</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>508</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>2762</v>
       </c>
       <c r="H14" t="n">
-        <v>28.07</v>
+        <v>46.19</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16510</v>
+        <v>242000</v>
       </c>
       <c r="K14" t="n">
-        <v>16380</v>
+        <v>241000</v>
       </c>
       <c r="L14" t="n">
-        <v>16440</v>
+        <v>249000</v>
       </c>
       <c r="M14" t="n">
-        <v>15750</v>
+        <v>226000</v>
       </c>
       <c r="N14" t="n">
-        <v>28.03</v>
+        <v>46.15</v>
       </c>
       <c r="O14" t="n">
-        <v>59514747620</v>
+        <v>4787571555500</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>15750</v>
+        <v>94500</v>
       </c>
       <c r="R14" t="n">
-        <v>-22000</v>
+        <v>-800000</v>
       </c>
       <c r="S14" t="n">
-        <v>-310000</v>
+        <v>-328000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표 호조에도 불구하고 주가 하락 지속. 외인 매수세는 꾸준히 유입.</t>
+          <t>노조, 임원진, 이재용 관련 비판적 언급 다수. 증여세 이슈로 인한 주가 하락 및 SK하이닉스와의 비교. 실적 대비 주가 부진 지적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '외인']</t>
+          <t>['이재용', '증여세', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,191 +1752,191 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>231750</v>
+        <v>4010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.24%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>511</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>2860</v>
+        <v>390</v>
       </c>
       <c r="H15" t="n">
-        <v>46.19</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>242000</v>
+        <v>4195</v>
       </c>
       <c r="K15" t="n">
-        <v>241000</v>
+        <v>4280</v>
       </c>
       <c r="L15" t="n">
-        <v>249000</v>
+        <v>4480</v>
       </c>
       <c r="M15" t="n">
-        <v>226000</v>
+        <v>3915</v>
       </c>
       <c r="N15" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4685092305750</v>
+        <v>167983816479</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-434000</v>
+        <v>-190000</v>
       </c>
       <c r="S15" t="n">
-        <v>-387000</v>
+        <v>6000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 관련 부정적 여론과 증여세 이슈 부각. 주가 부양 전략 부재 지적.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['증여세', '국정조사', '주주환원']</t>
+          <t>['5G', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4000</v>
+        <v>15770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="G16" t="n">
-        <v>391</v>
+        <v>582</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>15700</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>167251070868</v>
+        <v>63594801775</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>15700</v>
       </c>
       <c r="R16" t="n">
-        <v>-190000</v>
+        <v>403000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-468000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
+          <t>실적 발표 후 주가 하락세 지속. 실적 자체는 양호하나, 시장 상황 및 금리, 유가 변동성에 영향. 외국인 연일 매수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '글로벌 공급']</t>
+          <t>['실적 발표', '주가 하락', '외국인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56900</v>
+        <v>57100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.33%</t>
+          <t>'-7.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G17" t="n">
-        <v>2063</v>
+        <v>2131</v>
       </c>
       <c r="H17" t="n">
         <v>22.34</v>
@@ -1990,7 +1990,7 @@
         <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>370040607800</v>
+        <v>383185170450</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -1999,14 +1999,14 @@
         <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>-1454000</v>
+        <v>-1465000</v>
       </c>
       <c r="S17" t="n">
-        <v>-731000</v>
+        <v>-859000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>체코 원전 수주 관련 풍문 및 허위 기사로 인한 주가 하락. 회사 해명 공시에도 불신 지속.</t>
+          <t>체코 원전 사업 관련 부정적 보도 및 허위 기사 논란. 회사 해명 공시 요구. 일부 외인·기관 매수 관측.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['체코 원전', '풍문', '해명 공시']</t>
+          <t>['체코 원전', '해명 공시', '허위 기사']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24500</v>
+        <v>24075</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.24%</t>
+          <t>'-9.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>436</v>
+        <v>497</v>
       </c>
       <c r="H18" t="n">
         <v>12.23</v>
@@ -2076,13 +2076,13 @@
         <v>26600</v>
       </c>
       <c r="M18" t="n">
-        <v>24350</v>
+        <v>23800</v>
       </c>
       <c r="N18" t="n">
         <v>12.3</v>
       </c>
       <c r="O18" t="n">
-        <v>76170217050</v>
+        <v>93297678150</v>
       </c>
       <c r="P18" t="n">
         <v>59300</v>
@@ -2091,14 +2091,14 @@
         <v>22000</v>
       </c>
       <c r="R18" t="n">
-        <v>-142000</v>
+        <v>-394000</v>
       </c>
       <c r="S18" t="n">
-        <v>-15000</v>
+        <v>-18000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 앞두고 부정적 전망 우세. 태양광 사업 부진 및 적자 전환 가능성 제기.</t>
+          <t>실적 발표 예정. 태양광 및 원전 관련 부정적 언급. 주가 하락 및 투기판이라는 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '적자 전환', '태양광']</t>
+          <t>['실적 발표', '주가 하락', '태양광']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1841</v>
+        <v>1877</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.33%</t>
+          <t>'-10.62%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>13940565468</v>
+        <v>14162769970</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2183,10 +2183,10 @@
         <v>810</v>
       </c>
       <c r="R19" t="n">
-        <v>-82000</v>
+        <v>-93000</v>
       </c>
       <c r="S19" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16820</v>
+        <v>17070</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-12.44%</t>
+          <t>'-11.14%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F20" t="n">
         <v>69</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>94636781465</v>
+        <v>99686055030</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2275,14 +2275,14 @@
         <v>11550</v>
       </c>
       <c r="R20" t="n">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 우려 및 주가 폭락 가능성 경고. 주포 이탈 및 투매 신호 감지.</t>
+          <t>보호예수 해제 물량 출회 우려로 인한 주가 급락 경고. 주포의 움직임에 대한 의구심.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '주포', '폭락']</t>
+          <t>['보호예수', '급락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11970</v>
+        <v>11890</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.12%</t>
+          <t>'-16.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G21" t="n">
-        <v>2383</v>
+        <v>2369</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>332464675225</v>
+        <v>336017969055</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2367,14 +2367,14 @@
         <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-695000</v>
+        <v>-757000</v>
       </c>
       <c r="S21" t="n">
-        <v>-1386000</v>
+        <v>-1461000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 협상 결렬에 따른 주가 하락. 정치권 개입 및 재협상 가능성에 대한 논란.</t>
+          <t>체코 원전 사업 재협상 관련 부정적 전망과 정치권 개입 의혹 제기. 외인 매수세에도 불구하고 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '협상', '정치권']</t>
+          <t>['체코 원전', '재협상', '정치권 개입']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2424,7 +2424,7 @@
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16890461592</v>
+        <v>16952803026</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2459,10 +2459,10 @@
         <v>865</v>
       </c>
       <c r="R22" t="n">
-        <v>-187000</v>
+        <v>-174000</v>
       </c>
       <c r="S22" t="n">
-        <v>-271000</v>
+        <v>-273000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261029_14.xlsx
+++ b/data/trending_integrated_20261029_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>5060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.57%</t>
+          <t>'+28.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>7689171280</v>
+        <v>7732571170</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9320</v>
+        <v>9270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.65%</t>
+          <t>'+16.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>136629468410</v>
+        <v>138141146610</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -762,13 +762,13 @@
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>116139452925</v>
+        <v>116797693075</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7850</v>
+        <v>7810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.37%</t>
+          <t>'+4.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>112448771695</v>
+        <v>113067119160</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1555000</v>
+        <v>1553000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.57%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="G6" t="n">
-        <v>1645</v>
+        <v>1702</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5721986952000</v>
+        <v>5839546393000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 상승에 대한 긍정적 전망. 삼성전자와의 차별화 언급. 외인 매수세 유입 확인.</t>
+          <t>자사주 매입 및 외국인 순매수세에 힘입어 주가 상승 기대감이 고조됨. 삼성전자와의 비교 분석이 두드러짐.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '주가 상승', '외인 매수']</t>
+          <t>['자사주매입', '외국인', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14760</v>
+        <v>14920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+3.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>133</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>56153129890</v>
+        <v>56901485700</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>의료 AI 관련 긍정적 뉴스에도 불구하고 주가 하락세 지속. 공매도 및 매물 출회 가능성 언급. 투자 주의 경고.</t>
+          <t>미국 의료 AI 섹터 강세에도 불구하고 주가 변동성이 크며, 공매도 및 단주 거래에 대한 우려가 있음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '주가 하락']</t>
+          <t>['의료AI', '공매도', '단주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="n">
         <v>1.77</v>
@@ -1162,7 +1162,7 @@
         <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>108165390300</v>
+        <v>108735600950</v>
       </c>
       <c r="P8" t="n">
         <v>59600</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>542000</v>
+        <v>541000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+1.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F9" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G9" t="n">
-        <v>1831</v>
+        <v>1854</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>531021923000</v>
+        <v>538830664500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15080</v>
+        <v>15110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" t="n">
-        <v>869</v>
+        <v>892</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>148433131745</v>
+        <v>150297546985</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타, 유리기판 관련 뉴스 및 미국장 상승 영향. 루멘텀 인수 가능성 및 연금 매집. 삼성·SK 품질 안정화 기술 기대.</t>
+          <t>메타버스 및 유리기판 관련 뉴스와 함께 루멘텀 인수 기대감이 부각되며 주가 상승 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '루멘텀', '품질 안정화']</t>
+          <t>['메타버스', '유리기판', '루멘텀']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>187200</v>
+        <v>187100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.53%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F11" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="H11" t="n">
         <v>75</v>
@@ -1438,7 +1438,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1353538517750</v>
+        <v>1379487865900</v>
       </c>
       <c r="P11" t="n">
         <v>243500</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63200</v>
+        <v>63100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F12" t="n">
         <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>172952677000</v>
+        <v>175806357200</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8930</v>
+        <v>8910</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.72%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
         <v>194</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>31020676725</v>
+        <v>31155135680</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1667,184 +1667,184 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>232500</v>
+        <v>4050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>2762</v>
+        <v>391</v>
       </c>
       <c r="H14" t="n">
-        <v>46.19</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>242000</v>
+        <v>4195</v>
       </c>
       <c r="K14" t="n">
-        <v>241000</v>
+        <v>4280</v>
       </c>
       <c r="L14" t="n">
-        <v>249000</v>
+        <v>4480</v>
       </c>
       <c r="M14" t="n">
-        <v>226000</v>
+        <v>3915</v>
       </c>
       <c r="N14" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4787571555500</v>
+        <v>168810964943</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>-800000</v>
+        <v>-190000</v>
       </c>
       <c r="S14" t="n">
-        <v>-328000</v>
+        <v>6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>노조, 임원진, 이재용 관련 비판적 언급 다수. 증여세 이슈로 인한 주가 하락 및 SK하이닉스와의 비교. 실적 대비 주가 부진 지적.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재용', '증여세', '실적']</t>
+          <t>['5G', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4010</v>
+        <v>232250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="G15" t="n">
-        <v>390</v>
+        <v>2861</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>46.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>242000</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>241000</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>249000</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>226000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>167983816479</v>
+        <v>4875205408500</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-800000</v>
       </c>
       <c r="S15" t="n">
-        <v>6000</v>
+        <v>-328000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
+          <t>이재용 증여세 이슈와 하이닉스와의 실적 격차에 대한 불만이 제기됨. 주주환원 결정 기대감도 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '글로벌 공급']</t>
+          <t>['증여세', '주주환원', '실적']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15770</v>
+        <v>15700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="F16" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="G16" t="n">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="H16" t="n">
         <v>28.07</v>
@@ -1892,19 +1892,19 @@
         <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>15700</v>
+        <v>15600</v>
       </c>
       <c r="N16" t="n">
         <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>63594801775</v>
+        <v>68067416500</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>15700</v>
+        <v>15600</v>
       </c>
       <c r="R16" t="n">
         <v>403000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락세 지속. 실적 자체는 양호하나, 시장 상황 및 금리, 유가 변동성에 영향. 외국인 연일 매수.</t>
+          <t>실적은 컨센 대비 상회했으나 주가 하락에 대한 불만이 제기되며, 조선주 내 비교 분석이 이루어짐.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '외국인 매수']</t>
+          <t>['실적', '컨센', '조선주']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57100</v>
+        <v>56800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.00%</t>
+          <t>'-7.49%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G17" t="n">
-        <v>2131</v>
+        <v>2214</v>
       </c>
       <c r="H17" t="n">
         <v>22.34</v>
@@ -1990,7 +1990,7 @@
         <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>383185170450</v>
+        <v>393336320050</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 부정적 보도 및 허위 기사 논란. 회사 해명 공시 요구. 일부 외인·기관 매수 관측.</t>
+          <t>허위 기사 및 풍문으로 인한 급락에 대한 해명 공시가 나왔으나, 투자자 불만이 고조됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['체코 원전', '해명 공시', '허위 기사']</t>
+          <t>['해명공시', '허위기사', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24075</v>
+        <v>24250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.83%</t>
+          <t>'-9.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="F18" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G18" t="n">
-        <v>497</v>
+        <v>576</v>
       </c>
       <c r="H18" t="n">
         <v>12.23</v>
@@ -2082,7 +2082,7 @@
         <v>12.3</v>
       </c>
       <c r="O18" t="n">
-        <v>93297678150</v>
+        <v>102563635475</v>
       </c>
       <c r="P18" t="n">
         <v>59300</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 예정. 태양광 및 원전 관련 부정적 언급. 주가 하락 및 투기판이라는 비판.</t>
+          <t>실적 발표 예정인 가운데, 적자 전환 및 어닝 쇼크에 대한 우려와 기대감이 혼재함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '태양광']</t>
+          <t>['실적발표', '어닝쇼크', '적자전환']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1877</v>
+        <v>1884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.62%</t>
+          <t>'-10.29%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>14162769970</v>
+        <v>14478013075</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17070</v>
+        <v>17180</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.14%</t>
+          <t>'-10.57%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>99686055030</v>
+        <v>101528734450</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 출회 우려로 인한 주가 급락 경고. 주포의 움직임에 대한 의구심.</t>
+          <t>보호예수 물량 해제 및 주가 하락에 대한 우려가 제기되며, 투자자 간 의견 대립이 심함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '주포']</t>
+          <t>['보호예수', '주가하락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11890</v>
+        <v>11880</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.68%</t>
+          <t>'-16.75%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G21" t="n">
-        <v>2369</v>
+        <v>2373</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>336017969055</v>
+        <v>339531286715</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.51%</t>
+          <t>'-17.90%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16952803026</v>
+        <v>17093870718</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>

--- a/data/trending_integrated_20261029_14.xlsx
+++ b/data/trending_integrated_20261029_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+28.59%</t>
+          <t>'+28.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>7732571170</v>
+        <v>8062160960</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9270</v>
+        <v>9360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.02%</t>
+          <t>'+17.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>138141146610</v>
+        <v>138857911150</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38200</v>
+        <v>38250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.77%</t>
+          <t>'+9.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>116797693075</v>
+        <v>117697022550</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7810</v>
+        <v>7840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.83%</t>
+          <t>'+5.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>113067119160</v>
+        <v>113442873555</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1553000</v>
+        <v>1552000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.44%</t>
+          <t>'+4.37%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G6" t="n">
-        <v>1702</v>
+        <v>1796</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5839546393000</v>
+        <v>5953131739000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인 순매수세에 힘입어 주가 상승 기대감이 고조됨. 삼성전자와의 비교 분석이 두드러짐.</t>
+          <t>자사주 매입 및 외국인 매수세에 따른 긍정적 전망. 삼성전자와 비교하며 강세 예상.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인', '주가']</t>
+          <t>['자사주 매입', '외국인 매수', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14920</v>
+        <v>14810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+2.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" t="n">
         <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>56901485700</v>
+        <v>57620981930</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1130,10 +1130,10 @@
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>79</v>
@@ -1162,7 +1162,7 @@
         <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>108735600950</v>
+        <v>109552218500</v>
       </c>
       <c r="P8" t="n">
         <v>59600</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>541000</v>
+        <v>542000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="F9" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G9" t="n">
-        <v>1854</v>
+        <v>1870</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>538830664500</v>
+        <v>547557669500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15110</v>
+        <v>15100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.87%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G10" t="n">
-        <v>892</v>
+        <v>920</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>150297546985</v>
+        <v>151210326255</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타버스 및 유리기판 관련 뉴스와 함께 루멘텀 인수 기대감이 부각되며 주가 상승 전망이 제기됨.</t>
+          <t>메타 및 유리기판 관련 뉴스 및 삼성전자 인수 기대감. 광통신 섹터 내 대장주로서 강세 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메타버스', '유리기판', '루멘텀']</t>
+          <t>['메타', '유리기판', '인수 기대']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>187100</v>
+        <v>63000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>602</v>
+        <v>731</v>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
+        <v>41.55</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>190100</v>
+        <v>62800</v>
       </c>
       <c r="K11" t="n">
-        <v>189400</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>197000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>180800</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>74.90000000000001</v>
+        <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1379487865900</v>
+        <v>178538000000</v>
       </c>
       <c r="P11" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>71000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-1382000</v>
+        <v>273000</v>
       </c>
       <c r="S11" t="n">
-        <v>-119000</v>
+        <v>-191000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 부정적 전망. 우선주 매입 소각 기대감 있으나 확정적이지 않음.</t>
+          <t>자사주 매입 지속 및 수주 공시 확인. 신고가 근접 종목으로 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '오너 리스크']</t>
+          <t>['자사주 매입', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63100</v>
+        <v>186800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.71%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>711</v>
+        <v>615</v>
       </c>
       <c r="H12" t="n">
-        <v>41.55</v>
+        <v>75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>64200</v>
+        <v>190100</v>
       </c>
       <c r="K12" t="n">
-        <v>64200</v>
+        <v>189400</v>
       </c>
       <c r="L12" t="n">
-        <v>65500</v>
+        <v>197000</v>
       </c>
       <c r="M12" t="n">
-        <v>62500</v>
+        <v>180800</v>
       </c>
       <c r="N12" t="n">
-        <v>41.01</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>175806357200</v>
+        <v>1414664388100</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>243500</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>71000</v>
       </c>
       <c r="R12" t="n">
-        <v>273000</v>
+        <v>-1382000</v>
       </c>
       <c r="S12" t="n">
-        <v>-191000</v>
+        <v>-119000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 소각 및 매입 지속. 수주 공시 및 신고가 도전 가능성 언급. 삼성전자 시설 투자 확대 수혜 기대.</t>
+          <t>오너 리스크 및 주주환원 결정 시점에 대한 불만. 우선주 매입 소각 언급 있으나 불확실성 강조.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 소각', '수주 공시', '삼성전자']</t>
+          <t>['오너 리스크', '주주환원', '우선주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8910</v>
+        <v>4085</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.37</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>194</v>
+        <v>409</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9180</v>
+        <v>4195</v>
       </c>
       <c r="K13" t="n">
-        <v>9200</v>
+        <v>4280</v>
       </c>
       <c r="L13" t="n">
-        <v>10900</v>
+        <v>4480</v>
       </c>
       <c r="M13" t="n">
-        <v>8730</v>
+        <v>3915</v>
       </c>
       <c r="N13" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="O13" t="n">
-        <v>31155135680</v>
+        <v>170794253858</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>-190000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['5G', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4050</v>
+        <v>8910</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>-0.37</v>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>391</v>
+        <v>194</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>0.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4195</v>
+        <v>9180</v>
       </c>
       <c r="K14" t="n">
-        <v>4280</v>
+        <v>9200</v>
       </c>
       <c r="L14" t="n">
-        <v>4480</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>3915</v>
+        <v>8730</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>168810964943</v>
+        <v>31250590630</v>
       </c>
       <c r="P14" t="n">
-        <v>8100</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>592</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-190000</v>
+        <v>-40000</v>
       </c>
       <c r="S14" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '글로벌 공급']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>232250</v>
+        <v>233000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-3.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="G15" t="n">
-        <v>2861</v>
+        <v>2769</v>
       </c>
       <c r="H15" t="n">
         <v>46.19</v>
@@ -1806,7 +1806,7 @@
         <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4875205408500</v>
+        <v>4971024692750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 증여세 이슈와 하이닉스와의 실적 격차에 대한 불만이 제기됨. 주주환원 결정 기대감도 존재.</t>
+          <t>이재용 구속 및 주주환원 불확실성에 대한 강한 불만 제기. 공시 관련 내용 언급 있으나 구체적 팩트 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['증여세', '주주환원', '실적']</t>
+          <t>['주주환원', '구속', '공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15700</v>
+        <v>15690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-4.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="H16" t="n">
         <v>28.07</v>
@@ -1898,7 +1898,7 @@
         <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>68067416500</v>
+        <v>69978760660</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56800</v>
+        <v>57200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.49%</t>
+          <t>'-6.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>534</v>
       </c>
       <c r="G17" t="n">
-        <v>2214</v>
+        <v>2234</v>
       </c>
       <c r="H17" t="n">
         <v>22.34</v>
@@ -1990,7 +1990,7 @@
         <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>393336320050</v>
+        <v>401045008150</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>허위 기사 및 풍문으로 인한 급락에 대한 해명 공시가 나왔으나, 투자자 불만이 고조됨.</t>
+          <t>허위 기사 및 풍문에 대한 해명 공시 확인. 계약 관련 긍정적 언급 있으나 일부 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['해명공시', '허위기사', '주가']</t>
+          <t>['해명 공시', '계약', '풍문']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,184 +2035,184 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24250</v>
+        <v>1906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.18%</t>
+          <t>'-9.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>224</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>576</v>
+        <v>166</v>
       </c>
       <c r="H18" t="n">
-        <v>12.23</v>
+        <v>5.35</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>26700</v>
+        <v>2100</v>
       </c>
       <c r="K18" t="n">
-        <v>26350</v>
+        <v>2120</v>
       </c>
       <c r="L18" t="n">
-        <v>26600</v>
+        <v>2130</v>
       </c>
       <c r="M18" t="n">
-        <v>23800</v>
+        <v>1824</v>
       </c>
       <c r="N18" t="n">
-        <v>12.3</v>
+        <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>102563635475</v>
+        <v>14797610827</v>
       </c>
       <c r="P18" t="n">
-        <v>59300</v>
+        <v>4980</v>
       </c>
       <c r="Q18" t="n">
-        <v>22000</v>
+        <v>810</v>
       </c>
       <c r="R18" t="n">
-        <v>-394000</v>
+        <v>-93000</v>
       </c>
       <c r="S18" t="n">
-        <v>-18000</v>
+        <v>15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 예정인 가운데, 적자 전환 및 어닝 쇼크에 대한 우려와 기대감이 혼재함.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적발표', '어닝쇼크', '적자전환']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1884</v>
+        <v>24050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.29%</t>
+          <t>'-9.93%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>253</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="G19" t="n">
-        <v>170</v>
+        <v>625</v>
       </c>
       <c r="H19" t="n">
-        <v>5.35</v>
+        <v>12.23</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2100</v>
+        <v>26700</v>
       </c>
       <c r="K19" t="n">
-        <v>2120</v>
+        <v>26350</v>
       </c>
       <c r="L19" t="n">
-        <v>2130</v>
+        <v>26600</v>
       </c>
       <c r="M19" t="n">
-        <v>1824</v>
+        <v>23800</v>
       </c>
       <c r="N19" t="n">
-        <v>5.07</v>
+        <v>12.3</v>
       </c>
       <c r="O19" t="n">
-        <v>14478013075</v>
+        <v>108119044850</v>
       </c>
       <c r="P19" t="n">
-        <v>4980</v>
+        <v>59300</v>
       </c>
       <c r="Q19" t="n">
-        <v>810</v>
+        <v>22000</v>
       </c>
       <c r="R19" t="n">
-        <v>-93000</v>
+        <v>-394000</v>
       </c>
       <c r="S19" t="n">
-        <v>15000</v>
+        <v>-18000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
+          <t>실적 발표 예정 속에서 투자 심리 위축. 태양광 및 원전 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트']</t>
+          <t>['실적 발표', '태양광', '원전']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17180</v>
+        <v>17030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-10.57%</t>
+          <t>'-11.35%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>101528734450</v>
+        <v>102578690340</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제 및 주가 하락에 대한 우려가 제기되며, 투자자 간 의견 대립이 심함.</t>
+          <t>보호예수 물량 출회에 따른 급락 우려. 주포 움직임 및 매도 압력에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '주가하락', '주포']</t>
+          <t>['보호예수', '급락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11880</v>
+        <v>11910</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.75%</t>
+          <t>'-16.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>353</v>
       </c>
       <c r="G21" t="n">
-        <v>2373</v>
+        <v>2390</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>339531286715</v>
+        <v>343365346375</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2110</v>
+        <v>2125</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.90%</t>
+          <t>'-17.32%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
         <v>173</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>17093870718</v>
+        <v>17149993804</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>

--- a/data/trending_integrated_20261029_14.xlsx
+++ b/data/trending_integrated_20261029_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>5090</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+28.84%</t>
+          <t>'+29.35%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>8062160960</v>
+        <v>8192198870</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -670,13 +670,13 @@
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>138857911150</v>
+        <v>140172781920</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38250</v>
+        <v>37950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.91%</t>
+          <t>'+9.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>117697022550</v>
+        <v>118758382325</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7840</v>
+        <v>15140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.23%</t>
+          <t>'+5.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>399</v>
       </c>
       <c r="H5" t="n">
-        <v>0.42</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7450</v>
+        <v>14390</v>
       </c>
       <c r="K5" t="n">
-        <v>7470</v>
+        <v>15450</v>
       </c>
       <c r="L5" t="n">
-        <v>9680</v>
+        <v>16290</v>
       </c>
       <c r="M5" t="n">
-        <v>7360</v>
+        <v>14040</v>
       </c>
       <c r="N5" t="n">
-        <v>1.46</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>113442873555</v>
+        <v>60219590725</v>
       </c>
       <c r="P5" t="n">
-        <v>10300</v>
+        <v>49800</v>
       </c>
       <c r="Q5" t="n">
-        <v>952</v>
+        <v>8180</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-273000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
+          <t>루닛, 템퍼스AI 및 미국 의료AI 섹터 급등에 따른 시초 상승 기대감. 다만, 차익 실현 매물 및 공매도 관련 부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광주 반도체', '테마주', '외국인 매수']</t>
+          <t>['의료AI', '급등', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1552000</v>
+        <v>7790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.37%</t>
+          <t>'+4.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-1.04</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>227</v>
       </c>
       <c r="F6" t="n">
-        <v>492</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
-        <v>1796</v>
+        <v>455</v>
       </c>
       <c r="H6" t="n">
-        <v>48.66</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1487000</v>
+        <v>7450</v>
       </c>
       <c r="K6" t="n">
-        <v>1511000</v>
+        <v>7470</v>
       </c>
       <c r="L6" t="n">
-        <v>1587000</v>
+        <v>9680</v>
       </c>
       <c r="M6" t="n">
-        <v>1479000</v>
+        <v>7360</v>
       </c>
       <c r="N6" t="n">
-        <v>48.61</v>
+        <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>5953131739000</v>
+        <v>113878377095</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>952</v>
       </c>
       <c r="R6" t="n">
-        <v>374000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-115000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인 매수세에 따른 긍정적 전망. 삼성전자와 비교하며 강세 예상.</t>
+          <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외국인 매수', '전망']</t>
+          <t>['광주 반도체', '테마주', '외국인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14810</v>
+        <v>1537000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.92%</t>
+          <t>'+3.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>134</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>491</v>
       </c>
       <c r="G7" t="n">
-        <v>393</v>
+        <v>1893</v>
       </c>
       <c r="H7" t="n">
-        <v>8.050000000000001</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14390</v>
+        <v>1487000</v>
       </c>
       <c r="K7" t="n">
-        <v>15450</v>
+        <v>1511000</v>
       </c>
       <c r="L7" t="n">
-        <v>16290</v>
+        <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>14040</v>
+        <v>1479000</v>
       </c>
       <c r="N7" t="n">
-        <v>8.109999999999999</v>
+        <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>57620981930</v>
+        <v>6060711879000</v>
       </c>
       <c r="P7" t="n">
-        <v>49800</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>8180</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>-273000</v>
+        <v>374000</v>
       </c>
       <c r="S7" t="n">
-        <v>-15000</v>
+        <v>-115000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 강세에도 불구하고 주가 변동성이 크며, 공매도 및 단주 거래에 대한 우려가 있음.</t>
+          <t>자사주 매입 및 공매도 방어 성공, 주주 친화 정책에 대한 긍정적 평가. SK하이닉스의 시장 지배력 강화 및 삼성전자와의 비교 우위.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '단주']</t>
+          <t>['자사주매입', '공매도', '주주친화']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29350</v>
+        <v>29000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.26%</t>
+          <t>'+1.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="n">
         <v>1.77</v>
@@ -1162,7 +1162,7 @@
         <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>109552218500</v>
+        <v>110382424675</v>
       </c>
       <c r="P8" t="n">
         <v>59600</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>542000</v>
+        <v>15050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>383</v>
+        <v>163</v>
       </c>
       <c r="F9" t="n">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>1870</v>
+        <v>978</v>
       </c>
       <c r="H9" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L9" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M9" t="n">
-        <v>512000</v>
+        <v>14600</v>
       </c>
       <c r="N9" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>547557669500</v>
+        <v>152401979225</v>
       </c>
       <c r="P9" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R9" t="n">
-        <v>-36000</v>
+        <v>-444000</v>
       </c>
       <c r="S9" t="n">
-        <v>35000</v>
+        <v>44000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
+          <t>메타 관련 뉴스 및 3분기 실적 전망에 대한 기대감. 루멘텀 인수 및 삼성전자 투자 가능성에 따른 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
+          <t>['메타', '실적전망', '루멘텀']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15100</v>
+        <v>536000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>161</v>
+        <v>385</v>
       </c>
       <c r="F10" t="n">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="G10" t="n">
-        <v>920</v>
+        <v>1878</v>
       </c>
       <c r="H10" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K10" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L10" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M10" t="n">
-        <v>14600</v>
+        <v>512000</v>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O10" t="n">
-        <v>151210326255</v>
+        <v>557759035000</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R10" t="n">
-        <v>-444000</v>
+        <v>-36000</v>
       </c>
       <c r="S10" t="n">
-        <v>44000</v>
+        <v>35000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타 및 유리기판 관련 뉴스 및 삼성전자 인수 기대감. 광통신 섹터 내 대장주로서 강세 전망.</t>
+          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메타', '유리기판', '인수 기대']</t>
+          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63000</v>
+        <v>62700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>731</v>
+        <v>755</v>
       </c>
       <c r="H11" t="n">
         <v>41.55</v>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>62800</v>
+        <v>64200</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>64200</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>62500</v>
       </c>
       <c r="N11" t="n">
         <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>178538000000</v>
+        <v>182687426250</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
         <v>273000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 지속 및 수주 공시 확인. 신고가 근접 종목으로 긍정적 흐름 기대.</t>
+          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입을 통한 주가 방어 및 수소 시대 성장 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수주 공시', '신고가']</t>
+          <t>['수주공시', '자사주매입', '수소시대']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>186800</v>
+        <v>185500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F12" t="n">
         <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H12" t="n">
         <v>75</v>
@@ -1530,7 +1530,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1414664388100</v>
+        <v>1450412930200</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>오너 리스크 및 주주환원 결정 시점에 대한 불만. 우선주 매입 소각 언급 있으나 불확실성 강조.</t>
+          <t>우선주 매입 소각 및 주주환원 결정 지연에 대한 불만. 오너 리스크와 허술한 IR 대응에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', '우선주']</t>
+          <t>['우선주', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4085</v>
+        <v>8890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>409</v>
+        <v>194</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4195</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>4280</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>4480</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>3915</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>170794253858</v>
+        <v>31375961780</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-190000</v>
+        <v>-40000</v>
       </c>
       <c r="S13" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '글로벌 공급']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,99 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8910</v>
+        <v>4050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>4195</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>4280</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>4480</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>3915</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>31250590630</v>
+        <v>171958576131</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>-40000</v>
+        <v>-190000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>보호예수 물량 폭탄 및 주가 폭락 우려. 허위 기사 논란과 주포의 의도에 대한 불신.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['보호예수', '폭락', '주포']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>233000</v>
+        <v>231500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.72%</t>
+          <t>'-4.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="G15" t="n">
-        <v>2769</v>
+        <v>2824</v>
       </c>
       <c r="H15" t="n">
         <v>46.19</v>
@@ -1806,7 +1806,7 @@
         <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4971024692750</v>
+        <v>5076565264750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 구속 및 주주환원 불확실성에 대한 강한 불만 제기. 공시 관련 내용 언급 있으나 구체적 팩트 부족.</t>
+          <t>이재용 증여세 관련 주주환원 결정 지연 및 컨퍼런스콜 부실에 대한 불만 고조. 2등 기업 전락 및 하이닉스와의 격차 확대 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주주환원', '구속', '공시']</t>
+          <t>['주주환원', '증여세', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15690</v>
+        <v>15630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.97%</t>
+          <t>'-5.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G16" t="n">
-        <v>616</v>
+        <v>663</v>
       </c>
       <c r="H16" t="n">
         <v>28.07</v>
@@ -1892,19 +1892,19 @@
         <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>15600</v>
+        <v>15570</v>
       </c>
       <c r="N16" t="n">
         <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>69978760660</v>
+        <v>74156745240</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>15600</v>
+        <v>15570</v>
       </c>
       <c r="R16" t="n">
         <v>403000</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>실적은 컨센 대비 상회했으나 주가 하락에 대한 불만이 제기되며, 조선주 내 비교 분석이 이루어짐.</t>
+          <t>호실적 및 수주에도 불구하고 주가 하락 지속에 대한 불만. 공매도 및 연기금 매수에도 하락세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '컨센', '조선주']</t>
+          <t>['실적', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57200</v>
+        <v>1949</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.84%</t>
+          <t>'-7.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>534</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>2234</v>
+        <v>172</v>
       </c>
       <c r="H17" t="n">
-        <v>22.34</v>
+        <v>5.35</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>61400</v>
+        <v>2100</v>
       </c>
       <c r="K17" t="n">
-        <v>60600</v>
+        <v>2120</v>
       </c>
       <c r="L17" t="n">
-        <v>60800</v>
+        <v>2130</v>
       </c>
       <c r="M17" t="n">
-        <v>53400</v>
+        <v>1824</v>
       </c>
       <c r="N17" t="n">
-        <v>22.32</v>
+        <v>5.07</v>
       </c>
       <c r="O17" t="n">
-        <v>401045008150</v>
+        <v>16031358522</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>4980</v>
       </c>
       <c r="Q17" t="n">
-        <v>53400</v>
+        <v>810</v>
       </c>
       <c r="R17" t="n">
-        <v>-1465000</v>
+        <v>-93000</v>
       </c>
       <c r="S17" t="n">
-        <v>-859000</v>
+        <v>15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>허위 기사 및 풍문에 대한 해명 공시 확인. 계약 관련 긍정적 언급 있으나 일부 부정적 의견도 존재.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['해명 공시', '계약', '풍문']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1906</v>
+        <v>56200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.24%</t>
+          <t>'-8.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>533</v>
       </c>
       <c r="G18" t="n">
-        <v>166</v>
+        <v>2262</v>
       </c>
       <c r="H18" t="n">
-        <v>5.35</v>
+        <v>22.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2100</v>
+        <v>61400</v>
       </c>
       <c r="K18" t="n">
-        <v>2120</v>
+        <v>60600</v>
       </c>
       <c r="L18" t="n">
-        <v>2130</v>
+        <v>60800</v>
       </c>
       <c r="M18" t="n">
-        <v>1824</v>
+        <v>53400</v>
       </c>
       <c r="N18" t="n">
-        <v>5.07</v>
+        <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>14797610827</v>
+        <v>409816633450</v>
       </c>
       <c r="P18" t="n">
-        <v>4980</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>810</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>-93000</v>
+        <v>-1465000</v>
       </c>
       <c r="S18" t="n">
-        <v>15000</v>
+        <v>-859000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
+          <t>허위 기사 및 풍문에 대한 해명 공시 발표 후 주가 회복 기대. 기자 고소 및 계약 관련 논란.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트']</t>
+          <t>['해명공시', '풍문', '계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24050</v>
+        <v>23750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-9.93%</t>
+          <t>'-11.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="F19" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G19" t="n">
-        <v>625</v>
+        <v>682</v>
       </c>
       <c r="H19" t="n">
         <v>12.23</v>
@@ -2168,13 +2168,13 @@
         <v>26600</v>
       </c>
       <c r="M19" t="n">
-        <v>23800</v>
+        <v>23750</v>
       </c>
       <c r="N19" t="n">
         <v>12.3</v>
       </c>
       <c r="O19" t="n">
-        <v>108119044850</v>
+        <v>118567122250</v>
       </c>
       <c r="P19" t="n">
         <v>59300</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>실적 발표 예정 속에서 투자 심리 위축. 태양광 및 원전 관련 부정적 언급 다수.</t>
+          <t>실적 발표 예정 및 태양광 산업 전망에 대한 엇갈린 시각. 적자 전환 및 주가 하락 우려와 매수 타이밍 논의.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광', '원전']</t>
+          <t>['실적발표', '태양광', '분할매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17030</v>
+        <v>16940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.35%</t>
+          <t>'-11.82%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>102578690340</v>
+        <v>103815552430</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회에 따른 급락 우려. 주포 움직임 및 매도 압력에 대한 부정적 전망.</t>
+          <t>보호예수 물량 출회에 따른 급락 및 투자자 손실 우려. 주포의 의도에 대한 불신과 추가 하락 가능성.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2311,184 +2311,184 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11910</v>
+        <v>2110</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.54%</t>
+          <t>'-17.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.23</v>
+        <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="F21" t="n">
-        <v>353</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
-        <v>2390</v>
+        <v>174</v>
       </c>
       <c r="H21" t="n">
-        <v>9.6</v>
+        <v>1.22</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14270</v>
+        <v>2570</v>
       </c>
       <c r="K21" t="n">
-        <v>14180</v>
+        <v>2500</v>
       </c>
       <c r="L21" t="n">
-        <v>14180</v>
+        <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>10930</v>
+        <v>2080</v>
       </c>
       <c r="N21" t="n">
-        <v>9.83</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>343365346375</v>
+        <v>17302856594</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>2965</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>865</v>
       </c>
       <c r="R21" t="n">
-        <v>-757000</v>
+        <v>-174000</v>
       </c>
       <c r="S21" t="n">
-        <v>-1461000</v>
+        <v>-273000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 재협상 관련 부정적 전망과 정치권 개입 의혹 제기. 외인 매수세에도 불구하고 주가 하락세 지속.</t>
+          <t>급격한 주가 하락 및 롤링 현상에 대한 불만.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '재협상', '정치권 개입']</t>
+          <t>['주가 급락', '롤링', '사기']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2125</v>
+        <v>11610</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.32%</t>
+          <t>'-18.64%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>351</v>
       </c>
       <c r="G22" t="n">
-        <v>173</v>
+        <v>2399</v>
       </c>
       <c r="H22" t="n">
-        <v>1.22</v>
+        <v>9.6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2570</v>
+        <v>14270</v>
       </c>
       <c r="K22" t="n">
-        <v>2500</v>
+        <v>14180</v>
       </c>
       <c r="L22" t="n">
-        <v>2575</v>
+        <v>14180</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>10930</v>
       </c>
       <c r="N22" t="n">
-        <v>1.69</v>
+        <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>17149993804</v>
+        <v>349798999975</v>
       </c>
       <c r="P22" t="n">
-        <v>2965</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-174000</v>
+        <v>-757000</v>
       </c>
       <c r="S22" t="n">
-        <v>-273000</v>
+        <v>-1461000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 롤링 현상에 대한 불만.</t>
+          <t>체코 원전 사업 재협상 관련 부정적 전망과 정치권 개입 의혹 제기. 외인 매수세에도 불구하고 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 급락', '롤링', '사기']</t>
+          <t>['체코 원전', '재협상', '정치권 개입']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
